--- a/resultado_conferencia.xlsx
+++ b/resultado_conferencia.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ADMITIDOS" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DEMITIDOS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AVISO_PREVIO" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AFASTADOS" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FERIAS" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="ADMITIDOS" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="DEMITIDOS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="AVISO_PREVIO" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="AFASTADOS" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="FERIAS" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ADMITIDOS'!$A$1:$F$8</definedName>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>ALEX GERODANY FERREIRA</t>
+          <t>ALEX GEORDANY FERREIRA</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">

--- a/resultado_conferencia.xlsx
+++ b/resultado_conferencia.xlsx
@@ -14,15 +14,15 @@
     <sheet name="FERIAS" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ADMITIDOS'!$A$1:$F$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ADMITIDOS'!$A$1:$F$158</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'ADMITIDOS'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'DEMITIDOS'!$A$1:$F$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'DEMITIDOS'!$A$1:$F$13</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'DEMITIDOS'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'AVISO_PREVIO'!$A$1:$G$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'AVISO_PREVIO'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AFASTADOS'!$A$1:$H$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AFASTADOS'!$A$1:$H$12</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'AFASTADOS'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'FERIAS'!$A$1:$F$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'FERIAS'!$A$1:$F$25</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'FERIAS'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -471,14 +471,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
     <col width="46" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -522,20 +522,20 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>GILSEMAR DA SILVA CONCEICAO</t>
+          <t>ALEXANDRA CAETANO</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>000036</t>
+          <t>000261</t>
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>44845</v>
+        <v>46198</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>AFASTADO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -547,25 +547,25 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>CONTAGEM</t>
+          <t>ARAXÁ</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>JEFERSON FERNANDES ROCHA</t>
+          <t>ANA FLAVIA VIANA</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>000167</t>
+          <t>000230</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
-        <v>41205</v>
+        <v>46028</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>AFASTADO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -577,25 +577,25 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>CONTAGEM</t>
+          <t>ARAXÁ</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>THIAGO ALVES FERREIRA</t>
+          <t>APARECIDA ANTONIA DE SOUSA DOR</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>000699</t>
+          <t>000079</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>44802</v>
+        <v>45096</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>NÃO INFORMADO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -607,21 +607,21 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>SERRA DO SALITRE</t>
+          <t>ARAXÁ</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>ALESSANDRA SANTOS</t>
+          <t>BARBARA EVELYN PARREIRAS DE RE</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>000059</t>
+          <t>000150</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>46196</v>
+        <v>45600</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -637,25 +637,25 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>SERRA DO SALITRE</t>
+          <t>ARAXÁ</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>HENRIQUE VICENTE FERREIRA</t>
+          <t>BRUNA CRISTINA DOS SANTOS ARAU</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>000060</t>
+          <t>000147</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>46210</v>
+        <v>45580</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>AFASTADO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -667,21 +667,21 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>SERRA DO SALITRE</t>
+          <t>ARAXÁ</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>OTAVIO GABRIEL MENDES FERREIRA</t>
+          <t>CAMILA RIBEIRO ROCHA</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>000030</t>
+          <t>000267</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>45638</v>
+        <v>46219</v>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
@@ -697,35 +697,4535 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>ARAXÁ</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>CLAUDIO MANOEL COSTA</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>000226</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>ARAXÁ</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>DIEGO HENRIQUE DOS REIS LIMA</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>000255</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>46154</v>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>ARAXÁ</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>DIOGO COSME VIEIRA</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>000251</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>46136</v>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>ARAXÁ</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>DOUGLAS OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>000263</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>46210</v>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>ARAXÁ</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>ELISABETE SANTOS FLAVIO</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>000250</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>46135</v>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>ARAXÁ</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>ELIZABETE DOS REIS MARTINS</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>000168</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>45748</v>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>ARAXÁ</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>FABIO HENRIQUE DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>000276</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>46274</v>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>ARAXÁ</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>GABRIEL MACEDO PEREIRA</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>000264</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>46210</v>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>ARAXÁ</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>GILSEMAR DA SILVA CONCEICAO</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>000036</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>44845</v>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>AFASTADO</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>ARAXÁ</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>JOAO VICTOR FRERES MORAIS</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>000272</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>46247</v>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>ARAXÁ</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>LAIZA TATIELY DE ASSIS BARROS</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>000184</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>45852</v>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>ARAXÁ</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>LUAN RAFAEL DA SILVA NASCIMENT</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>000253</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>46142</v>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>ARAXÁ</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>LUCAS ANTUNES E SILVA</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>000169</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>45748</v>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>ARAXÁ</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>LUCAS RAFAEL CARNEIRO DA SILVA</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>000233</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>46035</v>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>ARAXÁ</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>PEDRO HENRIQUE ALVES DA SILVA</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>000278</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>ARAXÁ</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>SAMARA DA SILVA</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>000243</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>46093</v>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>ARAXÁ</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>SAMUEL ALVES MARTINS</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>000247</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>46125</v>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>ARAXÁ</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>SILVANO MILIONE</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>000279</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>46294</v>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>ARAXÁ</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>SIRLENNE MARTINS DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>000277</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>ARAXÁ</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>TARICK ALEXANDRE DIAS MACHADO</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>000275</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>46274</v>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>ARAXÁ</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>WAGNER DA SILVA REZENDE</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>000270</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>ARAXÁ</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>YASMIN MARQUES FERNANDES</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>000185</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>45852</v>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>CONSELHEIRO LAFAIETE</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>ALEXANDRE DE SOUZA TEIXEIRA</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>000206</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>46161</v>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>CONSELHEIRO LAFAIETE</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>ALEXIA AMANDA VIEIRA DA PAIXAO</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>000252</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>46252</v>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>CONSELHEIRO LAFAIETE</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>ANA PAULA SOTERO</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>000235</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>46191</v>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>CONSELHEIRO LAFAIETE</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>ANA VITORIA SILVA DE SOUZA</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>000245</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>46237</v>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>CONSELHEIRO LAFAIETE</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>ANDERSON MARQUES DA SILVA</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>000212</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>46162</v>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>CONSELHEIRO LAFAIETE</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>ANDRE DE SOUZA TEIXEIRA</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>000196</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>46161</v>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>CONSELHEIRO LAFAIETE</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>ANDRE MAX CUNHA DE ALMEIDA</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>000272</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>46303</v>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>CONSELHEIRO LAFAIETE</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>ANGELITA RAIMUNDA DO NASCIMENT</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>000208</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>46162</v>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>CONSELHEIRO LAFAIETE</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>ANJARA APARECIDA DE FATIMA</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>000197</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>46161</v>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>CONSELHEIRO LAFAIETE</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>CHRISTIAN DRUMOND CORDEIRO</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>000180</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>46156</v>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>CONSELHEIRO LAFAIETE</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>CLEIDE HELENA DO NASCIMENTO AZ</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>000217</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>46167</v>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>CONSELHEIRO LAFAIETE</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>CRISTIAN EMANUEL DE ASSIS REIS</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>000273</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>46308</v>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>CONSELHEIRO LAFAIETE</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>DANILO JOSE DE CARVALHO</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>000230</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>46184</v>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>CONSELHEIRO LAFAIETE</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>EDSON DIAS REIS</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>000220</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>46167</v>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>CONSELHEIRO LAFAIETE</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>ELLEN CRISTINE GOMES</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>000182</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>46156</v>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>CONSELHEIRO LAFAIETE</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>EMILENE DE SOUZA ROSA</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>000181</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>46156</v>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>CONSELHEIRO LAFAIETE</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>ERIKA DOS SANTOS DUARTE CARVAL</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>000236</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>46191</v>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>CONSELHEIRO LAFAIETE</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>EZEQUIAS DO CARMO PINHEIRO</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>000207</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>46161</v>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>CONSELHEIRO LAFAIETE</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>FABIANO FERREIRA CORDEIRO</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>000201</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>46161</v>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>CONSELHEIRO LAFAIETE</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>FELIPE LINS PEREIRA</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>000253</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="n">
+        <v>46254</v>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>CONSELHEIRO LAFAIETE</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>GABRIEL DE SOUZA VARGAS</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>000227</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>46175</v>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>CONSELHEIRO LAFAIETE</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>GEOVANIO MOREIRA</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>000234</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="n">
+        <v>46191</v>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>CONSELHEIRO LAFAIETE</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>GESSILENE DE FATIMA ALBERTO DE</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>000183</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>46156</v>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>CONSELHEIRO LAFAIETE</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>GIOVANA DE LOURDES ALBERTO</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>000251</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="n">
+        <v>46253</v>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>CONSELHEIRO LAFAIETE</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>GUSTAVO DE MELO COSTA</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>000213</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>46162</v>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>CONSELHEIRO LAFAIETE</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>JOHNNY WENDERSON DA SILVA</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>000255</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="n">
+        <v>46273</v>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>CONSELHEIRO LAFAIETE</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>JORDAN CRESCENCIO CAMPOS</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>000243</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>46224</v>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>CONSELHEIRO LAFAIETE</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>JOSIANE MARIA DE JESUS LANA</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>000130</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="n">
+        <v>46148</v>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>CONSELHEIRO LAFAIETE</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>KELY APARECIDA DE JESUS NARCIS</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>000237</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>CONSELHEIRO LAFAIETE</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>KIRLEI MATOS ALMEIDA</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>000228</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="n">
+        <v>46175</v>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>CONSELHEIRO LAFAIETE</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>LIVIA DALLA VEDOVA DAMASCENO</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>000248</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>46237</v>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>CONSELHEIRO LAFAIETE</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>LUDMILA CRISTINA CORDEIRO SILV</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>000246</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="n">
+        <v>46237</v>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>CONSELHEIRO LAFAIETE</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>MARCOS HENRIQUE DE SOUZA FERNA</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>000233</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>46191</v>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>CONSELHEIRO LAFAIETE</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>MARIA DO ROSARIO SANTOS</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>000218</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="n">
+        <v>46167</v>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>CONSELHEIRO LAFAIETE</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>MARINA DA CRUZ SANTOS</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>000198</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>46161</v>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>CONSELHEIRO LAFAIETE</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>MARINALVA PORTO DA CRUZ DOS SA</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>000219</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="n">
+        <v>46167</v>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>CONSELHEIRO LAFAIETE</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>MATHEUS RODRIGUES OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>000232</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>46184</v>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>CONSELHEIRO LAFAIETE</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>PEDRO PAULO DA SILVA MOREIRA</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>000271</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="n">
+        <v>46303</v>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>CONSELHEIRO LAFAIETE</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>ROGELSON ALMEIDA GONCALVES JUN</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>000179</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>46156</v>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>CONSELHEIRO LAFAIETE</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>ROGER BRAGA RIBEIRO</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>000184</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="n">
+        <v>46156</v>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>CONSELHEIRO LAFAIETE</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>ROSANGELA APARECIDA DOS REIS</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>000209</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>46162</v>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>CONSELHEIRO LAFAIETE</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>ROSANGELA DA CRUZ DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>000221</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="n">
+        <v>46167</v>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>CONSELHEIRO LAFAIETE</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>ROSEMERE DE JESUS ARRUDA</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>000216</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>46167</v>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>CONSELHEIRO LAFAIETE</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>SILAS PEREIRA DE MIRANDA</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>000264</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="n">
+        <v>46289</v>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>CONSELHEIRO LAFAIETE</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>THAIS SANTOS GOMES</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>000132</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>46148</v>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>CONSELHEIRO LAFAIETE</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>VERONICA SANTOS SEABRA</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>000199</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="n">
+        <v>46161</v>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>CONSELHEIRO LAFAIETE</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>VINICIUS ANTONIO DE PAULA GERA</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>000226</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>46175</v>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>CONSELHEIRO LAFAIETE</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>WELLINGTON DE DEUS REZENDE</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>000250</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="n">
+        <v>46247</v>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>CONSELHEIRO LAFAIETE</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>YURI RIAN PEDERIVA</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>000231</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>46184</v>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>ADMILSON PEREIRA LOPES</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>001015</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="n">
+        <v>46238</v>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>AGATHA MARTINS RAMOS</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>000921</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>45859</v>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>ALEXANDER ARCANJO</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>000670</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="n">
+        <v>44690</v>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>ALEXANDRE RAMOS DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>001044</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>46303</v>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>ALICYA GABRIELLE PEREIRA SILVA</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>001018</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="n">
+        <v>46237</v>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>AMANDA RODRIGUES DE SOUZA</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>000906</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>45509</v>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>ANA LETICIA DE FREITAS ROCHA</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>000968</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="n">
+        <v>46072</v>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>ANDREZA FREITAS SOUZA SANTOS</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>000972</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>46098</v>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>ARTHUR LUCAS SILVA LEITE</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>000864</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="n">
+        <v>45680</v>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>BRENO PEREIRA DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>000794</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>45335</v>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>BRUNO LOPES DO CARMO</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>001046</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="n">
+        <v>46303</v>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>CLAUDIO OLIVEIRA DO CARMO</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>000870</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="n">
+        <v>45692</v>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>DARLEY SILVA VIANA</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>000746</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="n">
+        <v>45117</v>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>DHONATAN MATIAS VIEIRA</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>000910</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="n">
+        <v>45215</v>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>ELEXSINALDO JOSE DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>001031</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="n">
+        <v>46282</v>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>ESTHER RAFAELA SOARES VERCIANO</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>001019</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>FABIO JOSE DOS REIS</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>001024</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="n">
+        <v>46261</v>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>FRANK NATORIO NASCIMENTO</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>000642</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>44572</v>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>FRANSOELE NAIARA SILVA CUNHA</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>000983</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="n">
+        <v>46147</v>
+      </c>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>GABRIELA SILVA SOARES</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>000974</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="n">
+        <v>46105</v>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>GASPARINO JOSE DA COSTA</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>001045</t>
+        </is>
+      </c>
+      <c r="D99" s="5" t="n">
+        <v>46303</v>
+      </c>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>HENRIQUE DA SILVA DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>000958</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="n">
+        <v>46030</v>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>INGRID DIAS DE OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>000953</t>
+        </is>
+      </c>
+      <c r="D101" s="5" t="n">
+        <v>46006</v>
+      </c>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F101" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>IZAIAS LUIZ FERREIRA</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>000927</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="n">
+        <v>45891</v>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>JEFERSON FERNANDES ROCHA</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t>000167</t>
+        </is>
+      </c>
+      <c r="D103" s="5" t="n">
+        <v>41205</v>
+      </c>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>AFASTADO</t>
+        </is>
+      </c>
+      <c r="F103" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>JOAO PEDRO AUHAREK PENA</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>001017</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="n">
+        <v>46237</v>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>JOSE ANTONIO CARLOS</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>001016</t>
+        </is>
+      </c>
+      <c r="D105" s="5" t="n">
+        <v>46238</v>
+      </c>
+      <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F105" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>JOSE THARSSYS M MARINHO BARROS</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>000970</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>46079</v>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>KAMILLY DIAS CANDIDO</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>001003</t>
+        </is>
+      </c>
+      <c r="D107" s="5" t="n">
+        <v>46196</v>
+      </c>
+      <c r="E107" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F107" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>KELLEN RAYANE ALVES DE JESUS</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>000992</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="n">
+        <v>46184</v>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>KELLY CRISTINA DOS REIS LOPES</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>000937</t>
+        </is>
+      </c>
+      <c r="D109" s="5" t="n">
+        <v>45958</v>
+      </c>
+      <c r="E109" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F109" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>KIMBERLLY LOUBACK DA COSTA</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>000998</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="n">
+        <v>46195</v>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>LAIZA CRISTINA RODRIGUES CIMIN</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>001009</t>
+        </is>
+      </c>
+      <c r="D111" s="5" t="n">
+        <v>46189</v>
+      </c>
+      <c r="E111" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F111" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>LUIZ GUSTAVO MUNIZ ROQUE</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>000886</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="n">
+        <v>45736</v>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>MAICON GUIMARAES PEREIRA</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>001028</t>
+        </is>
+      </c>
+      <c r="D113" s="5" t="n">
+        <v>46273</v>
+      </c>
+      <c r="E113" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>MARCELO RODRIGUES DA SILVA</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>001022</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>MARIA DE FATIMA DE JESUS</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>000777</t>
+        </is>
+      </c>
+      <c r="D115" s="5" t="n">
+        <v>45231</v>
+      </c>
+      <c r="E115" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F115" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>MARIANA IRENE GODINHO MIRANDA</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>000952</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="n">
+        <v>46006</v>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>MATHEUS AUGUSTO PEREIRA LOPES</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>000936</t>
+        </is>
+      </c>
+      <c r="D117" s="5" t="n">
+        <v>45958</v>
+      </c>
+      <c r="E117" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F117" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>MATHEUS CIPRIANO ARAUJO</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>000813</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>MAYCON DOUGLAS DA SILVA CRUZ</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>000935</t>
+        </is>
+      </c>
+      <c r="D119" s="5" t="n">
+        <v>45958</v>
+      </c>
+      <c r="E119" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F119" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>MICHELLE DE CASSIA SANTOS</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>000982</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="n">
+        <v>45040</v>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="4" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t>NOEMI PEREIRA DE OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="inlineStr">
+        <is>
+          <t>000988</t>
+        </is>
+      </c>
+      <c r="D121" s="5" t="n">
+        <v>46161</v>
+      </c>
+      <c r="E121" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F121" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>PETRONIO CARLOS DE LIMA PIO</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>000987</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="n">
+        <v>46154</v>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="4" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>RAFAEL SILVA SANTOS</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t>001021</t>
+        </is>
+      </c>
+      <c r="D123" s="5" t="n">
+        <v>46247</v>
+      </c>
+      <c r="E123" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F123" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>RAMON MASCARENHAS ROTONDANO</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>000914</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="n">
+        <v>45790</v>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="4" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="B125" s="4" t="inlineStr">
+        <is>
+          <t>RENATO MARTINS COURA</t>
+        </is>
+      </c>
+      <c r="C125" s="4" t="inlineStr">
+        <is>
+          <t>001047</t>
+        </is>
+      </c>
+      <c r="D125" s="5" t="n">
+        <v>46304</v>
+      </c>
+      <c r="E125" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F125" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>SAVIO ALEXANDRE MARTINS DIAS O</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>000775</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="n">
+        <v>45222</v>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="4" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="B127" s="4" t="inlineStr">
+        <is>
+          <t>STEFANY RODRIGUES BITENCOURT</t>
+        </is>
+      </c>
+      <c r="C127" s="4" t="inlineStr">
+        <is>
+          <t>000973</t>
+        </is>
+      </c>
+      <c r="D127" s="5" t="n">
+        <v>46100</v>
+      </c>
+      <c r="E127" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F127" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>STHEPHANY CAROLINA FERREIRA FE</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>000712</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="n">
+        <v>44866</v>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="4" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
+          <t>VICTOR HUGO SANTANA LAINA</t>
+        </is>
+      </c>
+      <c r="C129" s="4" t="inlineStr">
+        <is>
+          <t>000961</t>
+        </is>
+      </c>
+      <c r="D129" s="5" t="n">
+        <v>46049</v>
+      </c>
+      <c r="E129" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F129" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>YAGO SOUZA GOMES</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>001010</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="n">
+        <v>46212</v>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
+          <t>YGOR FELIPE DA SILVA</t>
+        </is>
+      </c>
+      <c r="C131" s="4" t="inlineStr">
+        <is>
+          <t>000924</t>
+        </is>
+      </c>
+      <c r="D131" s="5" t="n">
+        <v>45883</v>
+      </c>
+      <c r="E131" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F131" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>SERRA DO SALITRE</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>ALESSANDRA SANTOS</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>000059</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="n">
+        <v>46196</v>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="4" t="inlineStr">
+        <is>
+          <t>SERRA DO SALITRE</t>
+        </is>
+      </c>
+      <c r="B133" s="4" t="inlineStr">
+        <is>
+          <t>ALEX MOREIRA DIAS</t>
+        </is>
+      </c>
+      <c r="C133" s="4" t="inlineStr">
+        <is>
+          <t>000057</t>
+        </is>
+      </c>
+      <c r="D133" s="5" t="n">
+        <v>46087</v>
+      </c>
+      <c r="E133" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F133" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>SERRA DO SALITRE</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>HENRIQUE VICENTE FERREIRA</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>000060</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="n">
+        <v>46210</v>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>AFASTADO</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="4" t="inlineStr">
+        <is>
+          <t>SERRA DO SALITRE</t>
+        </is>
+      </c>
+      <c r="B135" s="4" t="inlineStr">
+        <is>
+          <t>JOYCE FERNANDA DE LIMA SOUSA</t>
+        </is>
+      </c>
+      <c r="C135" s="4" t="inlineStr">
+        <is>
+          <t>000055</t>
+        </is>
+      </c>
+      <c r="D135" s="5" t="n">
+        <v>46077</v>
+      </c>
+      <c r="E135" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F135" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>SERRA DO SALITRE</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>OTAVIO GABRIEL MENDES FERREIRA</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>000030</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="n">
+        <v>45638</v>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="4" t="inlineStr">
+        <is>
+          <t>SERRA DO SALITRE</t>
+        </is>
+      </c>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
+          <t>SIMONE GOMES LIMA</t>
+        </is>
+      </c>
+      <c r="C137" s="4" t="inlineStr">
+        <is>
+          <t>000048</t>
+        </is>
+      </c>
+      <c r="D137" s="5" t="n">
+        <v>45917</v>
+      </c>
+      <c r="E137" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F137" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
           <t>SETE LAGOAS</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>ANDRA JESSICA APARECIDA MOURA</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>000148</t>
+        </is>
+      </c>
+      <c r="D138" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="4" t="inlineStr">
+        <is>
+          <t>SETE LAGOAS</t>
+        </is>
+      </c>
+      <c r="B139" s="4" t="inlineStr">
+        <is>
+          <t>BARBARA LETICIA DE JESUS GOMES</t>
+        </is>
+      </c>
+      <c r="C139" s="4" t="inlineStr">
+        <is>
+          <t>000146</t>
+        </is>
+      </c>
+      <c r="D139" s="5" t="n">
+        <v>45306</v>
+      </c>
+      <c r="E139" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F139" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>SETE LAGOAS</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>BRUNA DOS REIS PEREIRA</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>000187</t>
+        </is>
+      </c>
+      <c r="D140" s="3" t="n">
+        <v>46216</v>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="4" t="inlineStr">
+        <is>
+          <t>SETE LAGOAS</t>
+        </is>
+      </c>
+      <c r="B141" s="4" t="inlineStr">
+        <is>
+          <t>CRISTIANE MOREIRA DE BARROS</t>
+        </is>
+      </c>
+      <c r="C141" s="4" t="inlineStr">
+        <is>
+          <t>000182</t>
+        </is>
+      </c>
+      <c r="D141" s="5" t="n">
+        <v>46189</v>
+      </c>
+      <c r="E141" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F141" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>SETE LAGOAS</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>FLAVIA GONZAGA DO NASCIMENTO</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>000143</t>
+        </is>
+      </c>
+      <c r="D142" s="3" t="n">
+        <v>45229</v>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="4" t="inlineStr">
+        <is>
+          <t>SETE LAGOAS</t>
+        </is>
+      </c>
+      <c r="B143" s="4" t="inlineStr">
+        <is>
+          <t>GABRIEL WILKE MARTINS</t>
+        </is>
+      </c>
+      <c r="C143" s="4" t="inlineStr">
+        <is>
+          <t>000181</t>
+        </is>
+      </c>
+      <c r="D143" s="5" t="n">
+        <v>46182</v>
+      </c>
+      <c r="E143" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F143" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>SETE LAGOAS</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
         <is>
           <t>IGOR PEREIRA DE ANDRADE</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C144" s="2" t="inlineStr">
         <is>
           <t>000138</t>
         </is>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D144" s="3" t="n">
         <v>45026</v>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>ATIVO</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="4" t="inlineStr">
+        <is>
+          <t>SETE LAGOAS</t>
+        </is>
+      </c>
+      <c r="B145" s="4" t="inlineStr">
+        <is>
+          <t>JHONATHAN EVANGELISTA GONCALVE</t>
+        </is>
+      </c>
+      <c r="C145" s="4" t="inlineStr">
+        <is>
+          <t>000145</t>
+        </is>
+      </c>
+      <c r="D145" s="5" t="n">
+        <v>45302</v>
+      </c>
+      <c r="E145" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F145" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>SETE LAGOAS</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>LUCAS RAFAEL MOREIRA DA SILVA</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>000188</t>
+        </is>
+      </c>
+      <c r="D146" s="3" t="n">
+        <v>46216</v>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="4" t="inlineStr">
+        <is>
+          <t>SETE LAGOAS</t>
+        </is>
+      </c>
+      <c r="B147" s="4" t="inlineStr">
+        <is>
+          <t>LUCAS RODRIGO REIS DE OLIVEI</t>
+        </is>
+      </c>
+      <c r="C147" s="4" t="inlineStr">
+        <is>
+          <t>000049</t>
+        </is>
+      </c>
+      <c r="D147" s="5" t="n">
+        <v>43900</v>
+      </c>
+      <c r="E147" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F147" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>SETE LAGOAS</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>MATEUS FILIPE OLIVEIRA MACIEL</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>000122</t>
+        </is>
+      </c>
+      <c r="D148" s="3" t="n">
+        <v>44671</v>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="4" t="inlineStr">
+        <is>
+          <t>SETE LAGOAS</t>
+        </is>
+      </c>
+      <c r="B149" s="4" t="inlineStr">
+        <is>
+          <t>MATEUS SALES PIMENTEL</t>
+        </is>
+      </c>
+      <c r="C149" s="4" t="inlineStr">
+        <is>
+          <t>000147</t>
+        </is>
+      </c>
+      <c r="D149" s="5" t="n">
+        <v>45405</v>
+      </c>
+      <c r="E149" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F149" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>SETE LAGOAS</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>MAURILIO ALVES DE CARVALHO</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>000052</t>
+        </is>
+      </c>
+      <c r="D150" s="3" t="n">
+        <v>43929</v>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="4" t="inlineStr">
+        <is>
+          <t>SETE LAGOAS</t>
+        </is>
+      </c>
+      <c r="B151" s="4" t="inlineStr">
+        <is>
+          <t>MICHELINE BEBIANA PEREIRA CAST</t>
+        </is>
+      </c>
+      <c r="C151" s="4" t="inlineStr">
+        <is>
+          <t>000183</t>
+        </is>
+      </c>
+      <c r="D151" s="5" t="n">
+        <v>46192</v>
+      </c>
+      <c r="E151" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F151" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>SETE LAGOAS</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>PAULO ROBERTO DE OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>000055</t>
+        </is>
+      </c>
+      <c r="D152" s="3" t="n">
+        <v>43959</v>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="4" t="inlineStr">
+        <is>
+          <t>SETE LAGOAS</t>
+        </is>
+      </c>
+      <c r="B153" s="4" t="inlineStr">
+        <is>
+          <t>PEDRO AUGUSTO ROCHA PINTO</t>
+        </is>
+      </c>
+      <c r="C153" s="4" t="inlineStr">
+        <is>
+          <t>000178</t>
+        </is>
+      </c>
+      <c r="D153" s="5" t="n">
+        <v>46097</v>
+      </c>
+      <c r="E153" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F153" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>SETE LAGOAS</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>RODRIGO MATIAS DE OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>000027</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="n">
+        <v>43613</v>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="4" t="inlineStr">
+        <is>
+          <t>SETE LAGOAS</t>
+        </is>
+      </c>
+      <c r="B155" s="4" t="inlineStr">
+        <is>
+          <t>SIDNEI FRANCISCO DE MELO</t>
+        </is>
+      </c>
+      <c r="C155" s="4" t="inlineStr">
+        <is>
+          <t>000179</t>
+        </is>
+      </c>
+      <c r="D155" s="5" t="n">
+        <v>46119</v>
+      </c>
+      <c r="E155" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F155" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>SETE LAGOAS</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>STEPHANIE ROBERTA SOUZA DIAS</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>000186</t>
+        </is>
+      </c>
+      <c r="D156" s="3" t="n">
+        <v>46202</v>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="4" t="inlineStr">
+        <is>
+          <t>SETE LAGOAS</t>
+        </is>
+      </c>
+      <c r="B157" s="4" t="inlineStr">
+        <is>
+          <t>VANDERLEI ANTONIO DE MELO</t>
+        </is>
+      </c>
+      <c r="C157" s="4" t="inlineStr">
+        <is>
+          <t>000172</t>
+        </is>
+      </c>
+      <c r="D157" s="5" t="n">
+        <v>45937</v>
+      </c>
+      <c r="E157" s="4" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F157" s="4" t="inlineStr">
+        <is>
+          <t>NOVO - não consta em nenhuma aba da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>SETE LAGOAS</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>WILIAM DE JESUS MARQUES</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>000144</t>
+        </is>
+      </c>
+      <c r="D158" s="3" t="n">
+        <v>45278</v>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>ATIVO</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>NOVO - não consta em nenhuma aba da planilha</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F8"/>
+  <autoFilter ref="A1:F158"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -737,7 +5237,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -788,20 +5288,20 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>LUCAS SANTOS DE QUEIROZ</t>
+          <t>BRUNO NOGUEIRA LOURENÇO</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>000266</t>
+          <t>000133</t>
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>46210</v>
+        <v>45469</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>ARAXA - linha 77</t>
+          <t>ARAXA - linha 14</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -818,20 +5318,20 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>SERGIO JESUS DE SENA</t>
+          <t>GUILHERME RODRIGUES ALVES</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>000204</t>
+          <t>000177</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
-        <v>45939</v>
+        <v>45818</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>ARAXA - linha 66</t>
+          <t>ARAXA - linha 33</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -843,25 +5343,25 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>CONSELHEIRO LAFAIETE</t>
+          <t>ARAXÁ</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>EDUARDO BARBOSA CHAVES</t>
+          <t>LUCAS SANTOS DE QUEIROZ</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>000141</t>
+          <t>000266</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>46149</v>
+        <v>46210</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>CONSELHEIRO LAFAIETE - linha 57</t>
+          <t>ARAXA - linha 77</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -873,25 +5373,25 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>CONSELHEIRO LAFAIETE</t>
+          <t>ARAXÁ</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>KAIWAN VICTOR VIEIRA</t>
+          <t>SERGIO JESUS DE SENA</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>000003</t>
+          <t>000204</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>46136</v>
+        <v>45939</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>CONSELHEIRO LAFAIETE - linha 112</t>
+          <t>ARAXA - linha 66</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -908,20 +5408,20 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>RAFAEL MORAES BARBOSA</t>
+          <t>AGUINALDO DA SILVA</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>000050</t>
+          <t>000174</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>46142</v>
+        <v>46155</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>CONSELHEIRO LAFAIETE - linha 147</t>
+          <t>CONSELHEIRO LAFAIETE - linha 8</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -933,25 +5433,25 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>CONTAGEM</t>
+          <t>CONSELHEIRO LAFAIETE</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>RENATO MARTINS DA SILVA GOUVEIA</t>
+          <t>EDUARDO BARBOSA CHAVES</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>000005</t>
+          <t>000141</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>44273</v>
+        <v>46149</v>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>CONTAGEM - linha 97</t>
+          <t>CONSELHEIRO LAFAIETE - linha 57</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -963,35 +5463,185 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>CONSELHEIRO LAFAIETE</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>KAIWAN VICTOR VIEIRA</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>000003</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>46136</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>CONSELHEIRO LAFAIETE - linha 112</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>DESLIGADO - não consta em nenhum PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>CONSELHEIRO LAFAIETE</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>RAFAEL MORAES BARBOSA</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>000050</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>46142</v>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>CONSELHEIRO LAFAIETE - linha 147</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>DESLIGADO - não consta em nenhum PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>CAIM RENATO DO CARMO</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>001042</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>CONTAGEM - linha 123</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>DESLIGADO - não consta em nenhum PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>RENATO MARTINS DA SILVA GOUVEIA</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>000005</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>44273</v>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>CONTAGEM - linha 97</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>DESLIGADO - não consta em nenhum PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>WILLIAN LOURENCO DA SILVA</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>001012</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>46226</v>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>CONTAGEM - linha 118</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>DESLIGADO - não consta em nenhum PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
           <t>SERRA DO SALITRE</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>ALDAIR ANTONIO PEREIRA</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>000036</t>
         </is>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D13" s="5" t="n">
         <v>45797</v>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>SERRA DO SALITRE - linha 3</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>DESLIGADO - não consta em nenhum PDF</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F8"/>
+  <autoFilter ref="A1:F13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -1007,7 +5657,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
@@ -1055,24 +5705,24 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ARAXÁ</t>
+          <t>CONTAGEM</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>BRUNO NOGUEIRA LOURENÇO</t>
+          <t>EDUARDO GONÇALVES SILVA</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>000119</t>
+          <t>000593</t>
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>45469</v>
+        <v>44424</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>46302</v>
+        <v>46308</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -1088,33 +5738,33 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>ARAXÁ</t>
+          <t>CONTAGEM</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>GUILHERME RODRIGUES ALVES</t>
+          <t>KELLY CRISTINA DOS REIS LOPES</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>000177</t>
+          <t>000937</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
-        <v>45818</v>
+        <v>45958</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>46301</v>
+        <v>46288</v>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>INDENIZADO</t>
+          <t>TRABALHADO</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
     </row>
@@ -1131,7 +5781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1346,16 +5996,16 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>ERNANI JULIO DA SILVA</t>
+          <t>CLAUDINEIA APARECIDA PIMENTA</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>000579</t>
+          <t>000564</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>44013</v>
+        <v>44391</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -1386,16 +6036,16 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>GRAZIELLE DANUBIA DA SILVEIRA</t>
+          <t>ERNANI JULIO DA SILVA</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>000333</t>
+          <t>000579</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>41956</v>
+        <v>44013</v>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
@@ -1426,16 +6076,16 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>JEFERSON FERNANDES ROCHA</t>
+          <t>GRAZIELLE DANUBIA DA SILVEIRA</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>000167</t>
+          <t>000333</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>41205</v>
+        <v>41956</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
@@ -1444,11 +6094,19 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr"/>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -1458,16 +6116,16 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>LUIZ FERNANDO RODRIGUES ROCHA</t>
+          <t>JEFERSON FERNANDES ROCHA</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>000372</t>
+          <t>000167</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>42552</v>
+        <v>41205</v>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
@@ -1476,54 +6134,126 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>CONTAGEM</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>JUCIMAR ALEXANDRE DE SOUZA</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>000820</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>45439</v>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>AFASTADO</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>LUIZ FERNANDO RODRIGUES ROCHA</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>000372</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>42552</v>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>AFASTADO</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
           <t>SERRA DO SALITRE</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>HENRIQUE VICENTE FERREIRA</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>000060</t>
         </is>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>46210</v>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>AFASTADO</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H10"/>
+  <autoFilter ref="A1:H12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -1535,11 +6265,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
@@ -1586,22 +6316,22 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>ANDERSON DE SOUZA SENA</t>
+          <t>ANSELMO JOAQUIM FERREIRA</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>000181</t>
+          <t>000031</t>
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>45825</v>
+        <v>44826</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>46274</v>
+        <v>46308</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>46303</v>
+        <v>46337</v>
       </c>
     </row>
     <row r="3">
@@ -1612,22 +6342,22 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>REGINALDO GOMES DOS SANTOS</t>
+          <t>CLEONIS JOSE BERNARDES</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>000010</t>
+          <t>000016</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
         <v>44820</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>46281</v>
+        <v>46308</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>46310</v>
+        <v>46337</v>
       </c>
     </row>
     <row r="4">
@@ -1638,22 +6368,22 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>VICENTE DOS REIS GOMES</t>
+          <t>DAVIDY VASCONCELOS MELO DE SOUZA</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>000006</t>
+          <t>000195</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>44820</v>
+        <v>45915</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>46281</v>
+        <v>46308</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>46310</v>
+        <v>46337</v>
       </c>
     </row>
     <row r="5">
@@ -1664,100 +6394,100 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>WANDEIR HONORATO DE OLIVEIRA</t>
+          <t>JOSE ANTONIO FELISBERTO</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>000136</t>
+          <t>000009</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>45497</v>
+        <v>44820</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>46274</v>
+        <v>46308</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>46303</v>
+        <v>46337</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>CONTAGEM</t>
+          <t>ARAXÁ</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>AGNALDO GONÇALVES DOS SANTOS</t>
+          <t>MICHELE FARIA DE CASTRO</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>000768</t>
+          <t>000113</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>45168</v>
+        <v>45447</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>46274</v>
+        <v>46308</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>46303</v>
+        <v>46337</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>CONTAGEM</t>
+          <t>ARAXÁ</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>CRISTIANO IZAIAS MOREIRA BATISTA MELO CARVALHO</t>
+          <t>REGINALDO GOMES DOS SANTOS</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>000764</t>
+          <t>000010</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>45168</v>
+        <v>44820</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>46274</v>
+        <v>46281</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>46303</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>CONTAGEM</t>
+          <t>ARAXÁ</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>DOMICIANO BISNETO DE ASSIS</t>
+          <t>VICENTE DOS REIS GOMES</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>000495</t>
+          <t>000006</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>44004</v>
+        <v>44820</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>46275</v>
+        <v>46281</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>46304</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="9">
@@ -1768,22 +6498,22 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>EDUARDO GONÇALVES SILVA</t>
+          <t>ADERITON FREITAS DO VALE</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>000593</t>
+          <t>000757</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>44424</v>
+        <v>45134</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>46275</v>
+        <v>46308</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>46304</v>
+        <v>46337</v>
       </c>
     </row>
     <row r="10">
@@ -1794,22 +6524,22 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>JUCIMAR ALEXANDRE DE SOUZA</t>
+          <t>ALEXANDRE BARBOSA DA COSTA</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>000820</t>
+          <t>000546</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>45439</v>
+        <v>44343</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>46274</v>
+        <v>46308</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>46303</v>
+        <v>46337</v>
       </c>
     </row>
     <row r="11">
@@ -1820,22 +6550,22 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>ODAIR JOSE BELTOLDO</t>
+          <t>AMANDA RODRIGUES DE SOUZA</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>000673</t>
+          <t>000906</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>44694</v>
+        <v>45509</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>46274</v>
+        <v>46286</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>46303</v>
+        <v>46315</v>
       </c>
     </row>
     <row r="12">
@@ -1846,22 +6576,22 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>THIAGO ALVES FERREIRA</t>
+          <t>EDUARDO LUIZ DUARTE</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>000699</t>
+          <t>000415</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>44802</v>
+        <v>43327</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>46274</v>
+        <v>46308</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>46303</v>
+        <v>46337</v>
       </c>
     </row>
     <row r="13">
@@ -1872,182 +6602,338 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>WILDENBERG DAYRELL BENEDITO DA SILVA</t>
+          <t>MARCIONE APARECIDO MARTINS</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>000841</t>
+          <t>000556</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>45495</v>
+        <v>44368</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>46274</v>
+        <v>46308</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>46303</v>
+        <v>46337</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>SERRA DO SALITRE</t>
+          <t>CONTAGEM</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>GILMAR ROBERTO ALVES DO NASCIMENTO</t>
+          <t>OZIAS ROSA NUNES DA SILVA</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>000042</t>
+          <t>000701</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>45848</v>
+        <v>44805</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>46274</v>
+        <v>46308</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>46303</v>
+        <v>46337</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>SERRA DO SALITRE</t>
+          <t>CONTAGEM</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>MIZAEL BABO AUGUSTO</t>
+          <t>PEDRO HENRIQUE ANTUNES MORAIS</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>000018</t>
+          <t>000840</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>45469</v>
+        <v>45495</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>46274</v>
+        <v>46308</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>46303</v>
+        <v>46337</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>SETE LAGOAS</t>
+          <t>CONTAGEM</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>EDSON HENRIQUE COSTA ALMEIDA</t>
+          <t>TIAGO DA SILVA LIMA</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>000124</t>
+          <t>000603</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>44715</v>
+        <v>44482</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>46274</v>
+        <v>46308</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>46303</v>
+        <v>46337</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>SETE LAGOAS</t>
+          <t>CONTAGEM</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>JOSEMAR MOREIRA DE SOUSA</t>
+          <t>WALMIR ALVES MEIRELES</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>000103</t>
+          <t>000475</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>44431</v>
+        <v>43725</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>46274</v>
+        <v>46308</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>46303</v>
+        <v>46322</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>SETE LAGOAS</t>
+          <t>CONTAGEM</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>NACIEL LEMOS PEREIRA</t>
+          <t>WILLER RODRIGUES DUARTE</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>000014</t>
+          <t>000591</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>43581</v>
+        <v>44091</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>46274</v>
+        <v>46308</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>46303</v>
+        <v>46337</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
+          <t>SERRA DO SALITRE</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>ERCIO BATISTA RODRIGUES</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>000010</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>45482</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>46337</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>SERRA DO SALITRE</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>NATALIA MARQUES CLEMENTE</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>000019</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>45509</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>46337</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
           <t>SETE LAGOAS</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>RONALDO SILVA DE CARVALHO</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>000141</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>45084</v>
-      </c>
-      <c r="E19" s="5" t="n">
-        <v>46274</v>
-      </c>
-      <c r="F19" s="5" t="n">
-        <v>46303</v>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>DAVI DOS SANTOS TEIXEIRA</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>000154</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>45537</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>46337</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>SETE LAGOAS</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>HENRIQUE PEREIRA DE ALMEIDA</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>000020</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>43651</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>46337</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>SETE LAGOAS</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>MARCOS ANTONIO PEREIRA DA SILVA</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>000150</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>45509</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>46337</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>SETE LAGOAS</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>RAFAELA GONCALVES DA SILVA</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>000151</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>45517</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>46337</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>SETE LAGOAS</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>ROBERTO FLAVIO DA COSTA</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>000018</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>43630</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>46337</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F19"/>
+  <autoFilter ref="A1:F25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/resultado_conferencia.xlsx
+++ b/resultado_conferencia.xlsx
@@ -14,15 +14,15 @@
     <sheet name="FERIAS" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ADMITIDOS'!$A$1:$F$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ADMITIDOS'!$A$1:$F$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'ADMITIDOS'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'DEMITIDOS'!$A$1:$F$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'DEMITIDOS'!$A$1:$F$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'DEMITIDOS'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'AVISO_PREVIO'!$A$1:$G$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'AVISO_PREVIO'!$A$1:$G$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'AVISO_PREVIO'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AFASTADOS'!$A$1:$H$12</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'AFASTADOS'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'FERIAS'!$A$1:$F$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'FERIAS'!$A$1:$F$22</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'FERIAS'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -471,10 +471,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
@@ -517,25 +517,25 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ARAXÁ</t>
+          <t>CONTAGEM</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>GILSEMAR DA SILVA CONCEICAO</t>
+          <t>ALISSON DA SILVA RAMALHO</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>000036</t>
+          <t>001049</t>
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>44845</v>
+        <v>46309</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>AFASTADO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -547,21 +547,21 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>CONSELHEIRO LAFAIETE</t>
+          <t>CONTAGEM</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>CRISTIAN EMANUEL DE ASSIS REIS</t>
+          <t>CARLOS ROBERTO DE JESUS DORNAS</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>000273</t>
+          <t>001051</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
-        <v>46308</v>
+        <v>46310</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -577,21 +577,21 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>CONSELHEIRO LAFAIETE</t>
+          <t>CONTAGEM</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>PEDRO PAULO DA SILVA MOREIRA</t>
+          <t>GUILHERME LOPES FERREIRA</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>000271</t>
+          <t>001050</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>46303</v>
+        <v>46310</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -612,16 +612,16 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>ALEXANDRE RAMOS DOS SANTOS</t>
+          <t>WAGNER ANTONIO EVANGELISTA</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>001044</t>
+          <t>001048</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>46303</v>
+        <v>46309</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -642,16 +642,16 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>BRUNO LOPES DO CARMO</t>
+          <t>WELLERSON XAVIER FERREIRA</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>001046</t>
+          <t>001053</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>46303</v>
+        <v>46311</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>GASPARINO JOSE DA COSTA</t>
+          <t>WESTER GRAICK DE ALMEIDA</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>001045</t>
+          <t>001052</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>46303</v>
+        <v>46310</v>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
@@ -697,25 +697,25 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>CONTAGEM</t>
+          <t>SETE LAGOAS</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>JEFERSON FERNANDES ROCHA</t>
+          <t>IGOR PEREIRA DE ANDRADE</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>000167</t>
+          <t>000138</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>41205</v>
+        <v>45026</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>AFASTADO</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -727,21 +727,21 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>CONTAGEM</t>
+          <t>SETE LAGOAS</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>RENATO MARTINS COURA</t>
+          <t>ROGERIO SILVA ARAUJO</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>001047</t>
+          <t>000189</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>46304</v>
+        <v>46309</v>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
@@ -754,128 +754,8 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>SERRA DO SALITRE</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>ALESSANDRA SANTOS</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>000059</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>46196</v>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>ATIVO</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>NOVO - não consta em nenhuma aba da planilha</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>SERRA DO SALITRE</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>HENRIQUE VICENTE FERREIRA</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>000060</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>46210</v>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>AFASTADO</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>NOVO - não consta em nenhuma aba da planilha</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>SERRA DO SALITRE</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>OTAVIO GABRIEL MENDES FERREIRA</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>000030</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>45638</v>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>ATIVO</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>NOVO - não consta em nenhuma aba da planilha</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>SETE LAGOAS</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>IGOR PEREIRA DE ANDRADE</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>000138</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>45026</v>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>ATIVO</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>NOVO - não consta em nenhuma aba da planilha</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F13"/>
+  <autoFilter ref="A1:F9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -887,14 +767,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
     <col width="38" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -933,25 +813,25 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ARAXÁ</t>
+          <t>CONTAGEM</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>BRUNO NOGUEIRA LOURENÇO</t>
+          <t>EDUARDO GONÇALVES SILVA</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>000133</t>
+          <t>000593</t>
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>45469</v>
+        <v>44424</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>ARAXA - linha 14</t>
+          <t>CONTAGEM - linha 34</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -960,338 +840,8 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>ARAXÁ</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>GUILHERME RODRIGUES ALVES</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>000177</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="n">
-        <v>45818</v>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>ARAXA - linha 33</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>DESLIGADO - não consta em nenhum PDF</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>ARAXÁ</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>LUCAS SANTOS DE QUEIROZ</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>000266</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>46210</v>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>ARAXA - linha 77</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>DESLIGADO - não consta em nenhum PDF</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>ARAXÁ</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>SERGIO JESUS DE SENA</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>000204</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>45939</v>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>ARAXA - linha 66</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>DESLIGADO - não consta em nenhum PDF</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>CONSELHEIRO LAFAIETE</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>AGUINALDO DA SILVA</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>000174</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>46155</v>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>CONSELHEIRO LAFAIETE - linha 8</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>DESLIGADO - não consta em nenhum PDF</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>CONSELHEIRO LAFAIETE</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>EDUARDO BARBOSA CHAVES</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>000141</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>46149</v>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>CONSELHEIRO LAFAIETE - linha 57</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>DESLIGADO - não consta em nenhum PDF</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>CONSELHEIRO LAFAIETE</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>KAIWAN VICTOR VIEIRA</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>000003</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>46136</v>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>CONSELHEIRO LAFAIETE - linha 112</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>DESLIGADO - não consta em nenhum PDF</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>CONSELHEIRO LAFAIETE</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>RAFAEL MORAES BARBOSA</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>000050</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>46142</v>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>CONSELHEIRO LAFAIETE - linha 147</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>DESLIGADO - não consta em nenhum PDF</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>CONTAGEM</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>CAIM RENATO DO CARMO</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>001042</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>46294</v>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>CONTAGEM - linha 123</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>DESLIGADO - não consta em nenhum PDF</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>CONTAGEM</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>RENATO MARTINS DA SILVA GOUVEIA</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>000005</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>44273</v>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>CONTAGEM - linha 97</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>DESLIGADO - não consta em nenhum PDF</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>CONTAGEM</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>WILLIAN LOURENCO DA SILVA</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>001012</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>46226</v>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>CONTAGEM - linha 118</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>DESLIGADO - não consta em nenhum PDF</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>SERRA DO SALITRE</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>ALDAIR ANTONIO PEREIRA</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>000036</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>45797</v>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>SERRA DO SALITRE - linha 3</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>DESLIGADO - não consta em nenhum PDF</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F13"/>
+  <autoFilter ref="A1:F2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -1303,11 +853,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
@@ -1355,38 +905,102 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>CONTAGEM</t>
+          <t>CONSELHEIRO LAFAIETE</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>EDUARDO GONÇALVES SILVA</t>
+          <t>LEANDRO SANTIAGO DE AQUINO</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>000593</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>44424</v>
-      </c>
+          <t>000024</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n"/>
       <c r="E2" s="3" t="n">
-        <v>46308</v>
+        <v>46310</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
+          <t>TRABALHADO</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>NAYARA TARCIA PENIDO GUIMARAES</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>000863</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>45678</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>46314</v>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
           <t>INDENIZADO</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>SETE LAGOAS</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>IGOR PEREIRA DE ANDRADE</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>000138</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>45026</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>INDENIZADO</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>NÃO</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G2"/>
+  <autoFilter ref="A1:G4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -1501,7 +1115,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>GILSEMAR DA SILVA CONCEICAO</t>
+          <t>GILSEMAR DA SILVA</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -1519,11 +1133,19 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr"/>
-      <c r="H3" s="4" t="inlineStr"/>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>ARAXÁ</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1751,11 +1373,19 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr"/>
-      <c r="H9" s="4" t="inlineStr"/>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>CONTAGEM</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1863,11 +1493,19 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr"/>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>SERRA DO SALITRE</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H12"/>
@@ -1882,7 +1520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2058,53 +1696,53 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>ARAXÁ</t>
+          <t>CONTAGEM</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>REGINALDO GOMES DOS SANTOS</t>
+          <t>ADERITON FREITAS DO VALE</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>000010</t>
+          <t>000757</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>44820</v>
+        <v>45134</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>46281</v>
+        <v>46308</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>46310</v>
+        <v>46337</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>ARAXÁ</t>
+          <t>CONTAGEM</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>VICENTE DOS REIS GOMES</t>
+          <t>ALEXANDRE BARBOSA DA COSTA</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>000006</t>
+          <t>000546</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>44820</v>
+        <v>44343</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>46281</v>
+        <v>46308</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>46310</v>
+        <v>46337</v>
       </c>
     </row>
     <row r="9">
@@ -2115,16 +1753,16 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>ADERITON FREITAS DO VALE</t>
+          <t>EDUARDO LUIZ DUARTE</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>000757</t>
+          <t>000415</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>45134</v>
+        <v>43327</v>
       </c>
       <c r="E9" s="5" t="n">
         <v>46308</v>
@@ -2141,16 +1779,16 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>ALEXANDRE BARBOSA DA COSTA</t>
+          <t>MARCIONE APARECIDO MARTINS</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>000546</t>
+          <t>000556</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>44343</v>
+        <v>44368</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>46308</v>
@@ -2167,16 +1805,16 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>EDUARDO LUIZ DUARTE</t>
+          <t>OZIAS ROSA NUNES DA SILVA</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>000415</t>
+          <t>000701</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>43327</v>
+        <v>44805</v>
       </c>
       <c r="E11" s="5" t="n">
         <v>46308</v>
@@ -2193,16 +1831,16 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>MARCIONE APARECIDO MARTINS</t>
+          <t>PEDRO HENRIQUE ANTUNES MORAIS</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>000556</t>
+          <t>000840</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>44368</v>
+        <v>45495</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>46308</v>
@@ -2219,16 +1857,16 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>OZIAS ROSA NUNES DA SILVA</t>
+          <t>TIAGO DA SILVA LIMA</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>000701</t>
+          <t>000603</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>44805</v>
+        <v>44482</v>
       </c>
       <c r="E13" s="5" t="n">
         <v>46308</v>
@@ -2245,22 +1883,22 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>PEDRO HENRIQUE ANTUNES MORAIS</t>
+          <t>WALMIR ALVES MEIRELES</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>000840</t>
+          <t>000475</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>45495</v>
+        <v>43725</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>46308</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>46337</v>
+        <v>46322</v>
       </c>
     </row>
     <row r="15">
@@ -2271,16 +1909,16 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>TIAGO DA SILVA LIMA</t>
+          <t>WILLER RODRIGUES DUARTE</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>000603</t>
+          <t>000591</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>44482</v>
+        <v>44091</v>
       </c>
       <c r="E15" s="5" t="n">
         <v>46308</v>
@@ -2292,47 +1930,47 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>CONTAGEM</t>
+          <t>SERRA DO SALITRE</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>WALMIR ALVES MEIRELES</t>
+          <t>ERCIO BATISTA RODRIGUES</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>000475</t>
+          <t>000010</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>43725</v>
+        <v>45482</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>46308</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>46322</v>
+        <v>46337</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>CONTAGEM</t>
+          <t>SERRA DO SALITRE</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>WILLER RODRIGUES DUARTE</t>
+          <t>NATALIA MARQUES CLEMENTE</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>000591</t>
+          <t>000019</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>44091</v>
+        <v>45509</v>
       </c>
       <c r="E17" s="5" t="n">
         <v>46308</v>
@@ -2344,21 +1982,21 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>SERRA DO SALITRE</t>
+          <t>SETE LAGOAS</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>ERCIO BATISTA RODRIGUES</t>
+          <t>DAVI DOS SANTOS TEIXEIRA</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>000010</t>
+          <t>000154</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>45482</v>
+        <v>45537</v>
       </c>
       <c r="E18" s="3" t="n">
         <v>46308</v>
@@ -2370,21 +2008,21 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>SERRA DO SALITRE</t>
+          <t>SETE LAGOAS</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>NATALIA MARQUES CLEMENTE</t>
+          <t>HENRIQUE PEREIRA DE ALMEIDA</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>000019</t>
+          <t>000020</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>45509</v>
+        <v>43651</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>46308</v>
@@ -2401,16 +2039,16 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>DAVI DOS SANTOS TEIXEIRA</t>
+          <t>MARCOS ANTONIO PEREIRA DA SILVA</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>000154</t>
+          <t>000150</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>45537</v>
+        <v>45509</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>46308</v>
@@ -2427,16 +2065,16 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>HENRIQUE PEREIRA DE ALMEIDA</t>
+          <t>RAFAELA GONCALVES DA SILVA</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>000020</t>
+          <t>000151</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>43651</v>
+        <v>45517</v>
       </c>
       <c r="E21" s="5" t="n">
         <v>46308</v>
@@ -2453,16 +2091,16 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>MARCOS ANTONIO PEREIRA DA SILVA</t>
+          <t>ROBERTO FLAVIO DA COSTA</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>000150</t>
+          <t>000018</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>45509</v>
+        <v>43630</v>
       </c>
       <c r="E22" s="3" t="n">
         <v>46308</v>
@@ -2471,60 +2109,8 @@
         <v>46337</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>SETE LAGOAS</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>RAFAELA GONCALVES DA SILVA</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>000151</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="n">
-        <v>45517</v>
-      </c>
-      <c r="E23" s="5" t="n">
-        <v>46308</v>
-      </c>
-      <c r="F23" s="5" t="n">
-        <v>46337</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>SETE LAGOAS</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>ROBERTO FLAVIO DA COSTA</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>000018</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="n">
-        <v>43630</v>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>46308</v>
-      </c>
-      <c r="F24" s="3" t="n">
-        <v>46337</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F24"/>
+  <autoFilter ref="A1:F22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/resultado_conferencia.xlsx
+++ b/resultado_conferencia.xlsx
@@ -14,13 +14,13 @@
     <sheet name="FERIAS" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ADMITIDOS'!$A$1:$F$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ADMITIDOS'!$A$1:$E$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'ADMITIDOS'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'DEMITIDOS'!$A$1:$F$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'DEMITIDOS'!$A$1:$E$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'DEMITIDOS'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'AVISO_PREVIO'!$A$1:$G$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'AVISO_PREVIO'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AFASTADOS'!$A$1:$H$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AFASTADOS'!$A$1:$E$12</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'AFASTADOS'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'FERIAS'!$A$1:$F$22</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'FERIAS'!$1:$1</definedName>
@@ -471,15 +471,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="46" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -508,11 +507,6 @@
           <t>Status</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Situação</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -522,25 +516,20 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>ALISSON DA SILVA RAMALHO</t>
+          <t>ALEXSANDRO TELES FERREIRA</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>001049</t>
+          <t>000014</t>
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>46309</v>
+        <v>46286</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
           <t>ATIVO</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>NOVO - não consta em nenhuma aba da planilha</t>
         </is>
       </c>
     </row>
@@ -552,25 +541,20 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>CARLOS ROBERTO DE JESUS DORNAS</t>
+          <t>AMAURI FERNANDES PEREIRA</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>001051</t>
+          <t>001029</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
-        <v>46310</v>
+        <v>46274</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
           <t>ATIVO</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>NOVO - não consta em nenhuma aba da planilha</t>
         </is>
       </c>
     </row>
@@ -582,25 +566,20 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>GUILHERME LOPES FERREIRA</t>
+          <t>JENNIFER TALITA DINIZ</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>001050</t>
+          <t>001027</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>46310</v>
+        <v>46273</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>ATIVO</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>NOVO - não consta em nenhuma aba da planilha</t>
         </is>
       </c>
     </row>
@@ -612,150 +591,25 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>WAGNER ANTONIO EVANGELISTA</t>
+          <t>RENATO MARTINS DA SILVA GOUVEI</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>001048</t>
+          <t>000005</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>46309</v>
+        <v>44273</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
           <t>ATIVO</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>NOVO - não consta em nenhuma aba da planilha</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>CONTAGEM</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>WELLERSON XAVIER FERREIRA</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>001053</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>46311</v>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>ATIVO</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>NOVO - não consta em nenhuma aba da planilha</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>CONTAGEM</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>WESTER GRAICK DE ALMEIDA</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>001052</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>46310</v>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>ATIVO</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>NOVO - não consta em nenhuma aba da planilha</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>SETE LAGOAS</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>IGOR PEREIRA DE ANDRADE</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>000138</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>45026</v>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>ATIVO</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>NOVO - não consta em nenhuma aba da planilha</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>SETE LAGOAS</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>ROGERIO SILVA ARAUJO</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>000189</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>46309</v>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>ATIVO</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>NOVO - não consta em nenhuma aba da planilha</t>
-        </is>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F9"/>
+  <autoFilter ref="A1:E5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -767,15 +621,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
-    <col width="38" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -804,44 +657,9 @@
           <t>Aba / linha na planilha</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Situação</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>CONTAGEM</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>EDUARDO GONÇALVES SILVA</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>000593</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>44424</v>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>CONTAGEM - linha 34</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>DESLIGADO - não consta em nenhum PDF</t>
-        </is>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F2"/>
+  <autoFilter ref="A1:E1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -918,7 +736,9 @@
           <t>000024</t>
         </is>
       </c>
-      <c r="D2" s="3" t="n"/>
+      <c r="D2" s="3" t="n">
+        <v>46141</v>
+      </c>
       <c r="E2" s="3" t="n">
         <v>46310</v>
       </c>
@@ -929,7 +749,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
     </row>
@@ -962,7 +782,7 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
     </row>
@@ -1012,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1020,9 +840,6 @@
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1051,21 +868,6 @@
           <t>Status</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Está na planilha?</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Filial na planilha</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Mesma filial?</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1091,21 +893,6 @@
           <t>AFASTADO</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>ARAXÁ</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -1131,21 +918,6 @@
           <t>AFASTADO</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>ARAXÁ</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1171,21 +943,6 @@
           <t>AFASTADO</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>ARAXÁ</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -1211,21 +968,6 @@
           <t>AFASTADO</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>CONSELHEIRO LAFAIETE</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1251,21 +993,6 @@
           <t>AFASTADO</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>CONTAGEM</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -1291,21 +1018,6 @@
           <t>AFASTADO</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>CONTAGEM</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1331,21 +1043,6 @@
           <t>AFASTADO</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>CONTAGEM</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -1371,21 +1068,6 @@
           <t>AFASTADO</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>CONTAGEM</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1411,21 +1093,6 @@
           <t>AFASTADO</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>CONTAGEM</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -1451,21 +1118,6 @@
           <t>AFASTADO</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>CONTAGEM</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1491,24 +1143,9 @@
           <t>AFASTADO</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>SERRA DO SALITRE</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H12"/>
+  <autoFilter ref="A1:E12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>
